--- a/experiment status.xlsx
+++ b/experiment status.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="37">
   <si>
     <t xml:space="preserve">Models</t>
   </si>
@@ -115,6 +115,9 @@
     <t xml:space="preserve">query based</t>
   </si>
   <si>
+    <t xml:space="preserve">Running</t>
+  </si>
+  <si>
     <t xml:space="preserve">Black_1</t>
   </si>
   <si>
@@ -122,9 +125,6 @@
   </si>
   <si>
     <t xml:space="preserve">full attention network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Running</t>
   </si>
   <si>
     <t xml:space="preserve">Red_2</t>
@@ -146,6 +146,7 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -328,7 +329,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A6:S17"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27.85"/>
@@ -744,15 +745,6 @@
       <c r="F14" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="G14" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="H14" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" s="0" t="s">
-        <v>9</v>
-      </c>
       <c r="J14" s="0" t="s">
         <v>9</v>
       </c>
@@ -789,43 +781,13 @@
         <v>30</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="0" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="K15" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="L15" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="M15" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="N15" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="O15" s="0" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="Q15" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S15" s="0" t="s">
         <v>30</v>
@@ -833,60 +795,33 @@
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="0" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="I16" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K16" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="L16" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M16" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="N16" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="O16" s="0" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="Q16" s="0" t="s">
         <v>35</v>
       </c>
       <c r="S16" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B17" s="0" t="s">
         <v>29</v>

--- a/experiment status.xlsx
+++ b/experiment status.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="37">
   <si>
     <t xml:space="preserve">Models</t>
   </si>
@@ -115,9 +115,6 @@
     <t xml:space="preserve">query based</t>
   </si>
   <si>
-    <t xml:space="preserve">Running</t>
-  </si>
-  <si>
     <t xml:space="preserve">Black_1</t>
   </si>
   <si>
@@ -131,6 +128,9 @@
   </si>
   <si>
     <t xml:space="preserve">maml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auxiliary (Query) Done</t>
   </si>
 </sst>
 </file>
@@ -328,7 +328,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A6:S17"/>
+  <dimension ref="A6:S19"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.15"/>
@@ -745,6 +745,15 @@
       <c r="F14" s="0" t="s">
         <v>9</v>
       </c>
+      <c r="G14" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="0" t="s">
+        <v>9</v>
+      </c>
       <c r="J14" s="0" t="s">
         <v>9</v>
       </c>
@@ -781,13 +790,43 @@
         <v>30</v>
       </c>
       <c r="D15" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="K15" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="L15" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="M15" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="N15" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="O15" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q15" s="0" t="s">
         <v>31</v>
-      </c>
-      <c r="G15" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q15" s="0" t="s">
-        <v>32</v>
       </c>
       <c r="S15" s="0" t="s">
         <v>30</v>
@@ -795,38 +834,70 @@
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="L16" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="M16" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="N16" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="O16" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q16" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q16" s="0" t="s">
-        <v>35</v>
-      </c>
       <c r="S16" s="0" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="0" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G19" s="0" t="s">
         <v>36</v>
       </c>
     </row>

--- a/experiment status.xlsx
+++ b/experiment status.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="40">
   <si>
     <t xml:space="preserve">Models</t>
   </si>
@@ -37,6 +37,9 @@
     <t xml:space="preserve">slowly changing regression</t>
   </si>
   <si>
+    <t xml:space="preserve">ImageNet</t>
+  </si>
+  <si>
     <t xml:space="preserve">Colour</t>
   </si>
   <si>
@@ -55,6 +58,9 @@
     <t xml:space="preserve">Sky Blue_9</t>
   </si>
   <si>
+    <t xml:space="preserve">Running</t>
+  </si>
+  <si>
     <t xml:space="preserve">reinitialization based</t>
   </si>
   <si>
@@ -62,6 +68,9 @@
   </si>
   <si>
     <t xml:space="preserve">Yellow_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
   </si>
   <si>
     <t xml:space="preserve">regularization based</t>
@@ -328,7 +337,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A6:S19"/>
+  <dimension ref="A6:X19"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.15"/>
@@ -366,6 +375,9 @@
       </c>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
+      <c r="V6" s="0" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D7" s="1" t="n">
@@ -405,500 +417,545 @@
         <v>2</v>
       </c>
       <c r="Q7" s="0" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="V7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" s="0" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="K8" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="M8" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="N8" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="O8" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q8" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="S8" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="L8" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="M8" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="N8" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="O8" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q8" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="S8" s="0" t="s">
-        <v>8</v>
+      <c r="V8" s="0" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J9" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K9" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L9" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M9" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N9" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O9" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q9" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S9" s="0" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="V9" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="W9" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="X9" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J10" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K10" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L10" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M10" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N10" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O10" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q10" s="0" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="S10" s="0" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K11" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M11" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N11" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O11" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q11" s="0" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="S11" s="0" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="V11" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="W11" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="X11" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J12" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K12" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L12" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M12" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N12" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O12" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q12" s="0" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="S12" s="0" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="V12" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="W12" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="X12" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J13" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K13" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L13" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M13" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N13" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O13" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q13" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="S13" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J14" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K14" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L14" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M14" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N14" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O14" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q14" s="0" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="S14" s="0" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K15" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M15" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N15" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O15" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q15" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="S15" s="0" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="V15" s="0" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="0" t="s">
-        <v>29</v>
-      </c>
       <c r="C16" s="0" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J16" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K16" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L16" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M16" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N16" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O16" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q16" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="S16" s="0" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="V16" s="0" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="0" t="s">
-        <v>29</v>
-      </c>
       <c r="C17" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G19" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/experiment status.xlsx
+++ b/experiment status.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="41">
   <si>
     <t xml:space="preserve">Models</t>
   </si>
@@ -58,61 +58,64 @@
     <t xml:space="preserve">Sky Blue_9</t>
   </si>
   <si>
+    <t xml:space="preserve">reinitialization based</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cbp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yellow_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regularization based</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ewc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue_6</t>
+  </si>
+  <si>
     <t xml:space="preserve">Running</t>
   </si>
   <si>
-    <t xml:space="preserve">reinitialization based</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cbp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yellow_3</t>
+    <t xml:space="preserve">regenerative regularization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Done </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orange_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activation based</t>
+  </si>
+  <si>
+    <t xml:space="preserve">concat relu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purple_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replay based</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reservoir replay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chocolate_8</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>
   </si>
   <si>
-    <t xml:space="preserve">regularization based</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ewc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blue_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regenerative regularization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Done </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orange_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activation based</t>
-  </si>
-  <si>
-    <t xml:space="preserve">concat relu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purple_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replay based</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reservoir replay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chocolate_8</t>
-  </si>
-  <si>
     <t xml:space="preserve">dark experience replay</t>
   </si>
   <si>
     <t xml:space="preserve">Magenta_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lafda</t>
   </si>
   <si>
     <t xml:space="preserve">main model</t>
@@ -482,7 +485,13 @@
         <v>9</v>
       </c>
       <c r="V8" s="0" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="W8" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="X8" s="0" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -490,61 +499,61 @@
         <v>7</v>
       </c>
       <c r="B9" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="D9" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="K9" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="M9" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="N9" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="O9" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="I9" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="J9" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="K9" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="L9" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="M9" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="N9" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="O9" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q9" s="0" t="s">
-        <v>15</v>
-      </c>
       <c r="S9" s="0" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V9" s="0" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="W9" s="0" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="X9" s="0" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -552,51 +561,60 @@
         <v>7</v>
       </c>
       <c r="B10" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="K10" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="M10" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="N10" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="O10" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="I10" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="J10" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="K10" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="L10" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="M10" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="N10" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="O10" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q10" s="0" t="s">
-        <v>19</v>
-      </c>
       <c r="S10" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="V10" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="W10" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="X10" s="0" t="s">
         <v>18</v>
       </c>
     </row>
@@ -605,61 +623,52 @@
         <v>7</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C11" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="E11" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="K11" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="L11" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="M11" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="N11" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="O11" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q11" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="I11" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="K11" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="L11" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="M11" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="N11" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="O11" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q11" s="0" t="s">
-        <v>22</v>
-      </c>
       <c r="S11" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="V11" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="W11" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="X11" s="0" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -667,61 +676,61 @@
         <v>7</v>
       </c>
       <c r="B12" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="D12" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="K12" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="L12" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="M12" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="N12" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="O12" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="I12" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="J12" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="K12" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="L12" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="M12" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="N12" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="O12" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q12" s="0" t="s">
-        <v>25</v>
-      </c>
       <c r="S12" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V12" s="0" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="W12" s="0" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="X12" s="0" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -729,52 +738,58 @@
         <v>7</v>
       </c>
       <c r="B13" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="D13" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="I13" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="J13" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="K13" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="L13" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="M13" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="N13" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="O13" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q13" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="I13" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="J13" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="K13" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="L13" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="M13" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="N13" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="O13" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q13" s="0" t="s">
+      <c r="S13" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="V13" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="0" t="s">
-        <v>27</v>
+      <c r="W13" s="0" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -782,7 +797,7 @@
         <v>7</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>29</v>
@@ -829,16 +844,25 @@
       <c r="S14" s="0" t="s">
         <v>29</v>
       </c>
+      <c r="V14" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="W14" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="X14" s="0" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" s="0" t="s">
         <v>10</v>
@@ -877,24 +901,30 @@
         <v>10</v>
       </c>
       <c r="Q15" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="S15" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="S15" s="0" t="s">
-        <v>33</v>
-      </c>
       <c r="V15" s="0" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="W15" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="X15" s="0" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" s="0" t="s">
         <v>10</v>
@@ -933,29 +963,35 @@
         <v>10</v>
       </c>
       <c r="Q16" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="S16" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="S16" s="0" t="s">
-        <v>36</v>
-      </c>
       <c r="V16" s="0" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="W16" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="X16" s="0" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G19" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/experiment status.xlsx
+++ b/experiment status.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="41">
   <si>
     <t xml:space="preserve">Models</t>
   </si>
@@ -40,6 +40,9 @@
     <t xml:space="preserve">ImageNet</t>
   </si>
   <si>
+    <t xml:space="preserve">SCR_NEW</t>
+  </si>
+  <si>
     <t xml:space="preserve">Colour</t>
   </si>
   <si>
@@ -67,6 +70,12 @@
     <t xml:space="preserve">Yellow_3</t>
   </si>
   <si>
+    <t xml:space="preserve">Running</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Runing</t>
+  </si>
+  <si>
     <t xml:space="preserve">regularization based</t>
   </si>
   <si>
@@ -76,9 +85,6 @@
     <t xml:space="preserve">Blue_6</t>
   </si>
   <si>
-    <t xml:space="preserve">Running</t>
-  </si>
-  <si>
     <t xml:space="preserve">regenerative regularization</t>
   </si>
   <si>
@@ -106,16 +112,10 @@
     <t xml:space="preserve">Chocolate_8</t>
   </si>
   <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
     <t xml:space="preserve">dark experience replay</t>
   </si>
   <si>
     <t xml:space="preserve">Magenta_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lafda</t>
   </si>
   <si>
     <t xml:space="preserve">main model</t>
@@ -158,7 +158,6 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -340,7 +339,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A6:X19"/>
+  <dimension ref="A6:AB19"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.15"/>
@@ -381,6 +380,9 @@
       <c r="V6" s="0" t="s">
         <v>5</v>
       </c>
+      <c r="Z6" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D7" s="1" t="n">
@@ -420,7 +422,7 @@
         <v>2</v>
       </c>
       <c r="Q7" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V7" s="0" t="n">
         <v>0</v>
@@ -431,427 +433,511 @@
       <c r="X7" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="Z7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="J8" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="K8" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="L8" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="M8" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="N8" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="O8" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q8" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="S8" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="I8" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="J8" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="K8" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="L8" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="M8" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="N8" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="O8" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q8" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="S8" s="0" t="s">
-        <v>9</v>
-      </c>
       <c r="V8" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W8" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X8" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="Z8" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA8" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB8" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J9" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K9" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L9" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M9" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N9" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O9" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q9" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="S9" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="S9" s="0" t="s">
-        <v>13</v>
-      </c>
       <c r="V9" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W9" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X9" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="Z9" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA9" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB9" s="0" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J10" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K10" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L10" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M10" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N10" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O10" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q10" s="0" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="S10" s="0" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="V10" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W10" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X10" s="0" t="s">
-        <v>18</v>
+        <v>11</v>
+      </c>
+      <c r="Z10" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA10" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB10" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K11" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M11" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N11" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O11" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q11" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="S11" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="S11" s="0" t="s">
-        <v>19</v>
+      <c r="V11" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="W11" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="X11" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z11" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA11" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB11" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J12" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K12" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L12" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M12" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N12" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O12" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q12" s="0" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="S12" s="0" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="V12" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W12" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X12" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="Z12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA12" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB12" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J13" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K13" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L13" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M13" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N13" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O13" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q13" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="S13" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="V13" s="0" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="W13" s="0" t="s">
-        <v>28</v>
+        <v>11</v>
+      </c>
+      <c r="X13" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z13" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA13" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB13" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J14" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K14" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L14" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M14" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N14" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O14" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q14" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S14" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="S14" s="0" t="s">
-        <v>29</v>
-      </c>
       <c r="V14" s="0" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="W14" s="0" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="X14" s="0" t="s">
-        <v>31</v>
+        <v>11</v>
+      </c>
+      <c r="Z14" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA14" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB14" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -865,40 +951,40 @@
         <v>34</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K15" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M15" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N15" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O15" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q15" s="0" t="s">
         <v>35</v>
@@ -907,13 +993,22 @@
         <v>34</v>
       </c>
       <c r="V15" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W15" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X15" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="Z15" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA15" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB15" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -927,40 +1022,40 @@
         <v>37</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J16" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K16" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L16" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M16" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N16" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O16" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q16" s="0" t="s">
         <v>38</v>
@@ -969,13 +1064,22 @@
         <v>37</v>
       </c>
       <c r="V16" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W16" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X16" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="Z16" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA16" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB16" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/experiment status.xlsx
+++ b/experiment status.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="39">
   <si>
     <t xml:space="preserve">Models</t>
   </si>
@@ -68,12 +68,6 @@
   </si>
   <si>
     <t xml:space="preserve">Yellow_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Running</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Runing</t>
   </si>
   <si>
     <t xml:space="preserve">regularization based</t>
@@ -158,6 +152,7 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -579,10 +574,10 @@
         <v>11</v>
       </c>
       <c r="AA9" s="0" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AB9" s="0" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -590,52 +585,52 @@
         <v>8</v>
       </c>
       <c r="B10" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="J10" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="L10" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="M10" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="N10" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="O10" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q10" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="I10" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="J10" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="K10" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="L10" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="M10" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="N10" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="O10" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q10" s="0" t="s">
-        <v>20</v>
-      </c>
       <c r="S10" s="0" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="V10" s="0" t="s">
         <v>11</v>
@@ -661,52 +656,52 @@
         <v>8</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C11" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="J11" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="K11" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="L11" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="M11" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="N11" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="O11" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q11" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="I11" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="J11" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="K11" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="L11" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="M11" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="N11" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="O11" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q11" s="0" t="s">
-        <v>23</v>
-      </c>
       <c r="S11" s="0" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="V11" s="0" t="s">
         <v>11</v>
@@ -732,52 +727,52 @@
         <v>8</v>
       </c>
       <c r="B12" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="L12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="M12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="N12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="O12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q12" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="I12" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="J12" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="K12" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="L12" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="M12" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="N12" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="O12" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q12" s="0" t="s">
-        <v>26</v>
-      </c>
       <c r="S12" s="0" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="V12" s="0" t="s">
         <v>11</v>
@@ -792,10 +787,10 @@
         <v>11</v>
       </c>
       <c r="AA12" s="0" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AB12" s="0" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -803,52 +798,52 @@
         <v>8</v>
       </c>
       <c r="B13" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="J13" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="K13" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="L13" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="M13" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="N13" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="O13" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q13" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="I13" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="J13" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="K13" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="L13" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="M13" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="N13" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="O13" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q13" s="0" t="s">
-        <v>29</v>
-      </c>
       <c r="S13" s="0" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V13" s="0" t="s">
         <v>11</v>
@@ -874,10 +869,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D14" s="0" t="s">
         <v>11</v>
@@ -916,10 +911,10 @@
         <v>11</v>
       </c>
       <c r="Q14" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="S14" s="0" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="V14" s="0" t="s">
         <v>11</v>
@@ -942,55 +937,55 @@
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="D15" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="J15" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="K15" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="L15" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="M15" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="N15" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="O15" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q15" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="H15" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="I15" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="J15" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="K15" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="L15" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="M15" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="N15" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="O15" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q15" s="0" t="s">
-        <v>35</v>
-      </c>
       <c r="S15" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="V15" s="0" t="s">
         <v>11</v>
@@ -1013,55 +1008,55 @@
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="J16" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="K16" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="L16" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="M16" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="N16" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="O16" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q16" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="H16" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="I16" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="J16" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="K16" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="L16" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="M16" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="N16" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="O16" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q16" s="0" t="s">
-        <v>38</v>
-      </c>
       <c r="S16" s="0" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="V16" s="0" t="s">
         <v>11</v>
@@ -1084,18 +1079,18 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G19" s="0" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
